--- a/backend/数据模板/模板-计算机网络成绩考勤情况测试.xlsx
+++ b/backend/数据模板/模板-计算机网络成绩考勤情况测试.xlsx
@@ -30,9 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>编号</t>
+  </si>
+  <si>
+    <t>课程号</t>
   </si>
   <si>
     <t>课程名称</t>
@@ -1190,18 +1193,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ35"/>
+  <dimension ref="A1:AR35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="4.22727272727273" customWidth="1"/>
-    <col min="2" max="2" width="10.4181818181818" customWidth="1"/>
-    <col min="3" max="4" width="11.4363636363636" customWidth="1"/>
-    <col min="5" max="5" width="7.54545454545455" customWidth="1"/>
-    <col min="6" max="40" width="7.33636363636364" customWidth="1"/>
-    <col min="43" max="43" width="7.33636363636364" customWidth="1"/>
+    <col min="2" max="3" width="10.4181818181818" customWidth="1"/>
+    <col min="4" max="5" width="11.4363636363636" customWidth="1"/>
+    <col min="6" max="6" width="7.54545454545455" customWidth="1"/>
+    <col min="7" max="41" width="7.33636363636364" customWidth="1"/>
+    <col min="44" max="44" width="7.33636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="9.5" spans="1:43">
+    <row r="1" s="1" customFormat="1" ht="9.5" spans="1:44">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1217,7 +1220,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -1331,17 +1334,20 @@
       <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" ht="16.35" customHeight="1" spans="1:43">
+      <c r="AR1" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" ht="16.35" customHeight="1" spans="1:44">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -1372,41 +1378,42 @@
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="4"/>
-      <c r="AL2" s="4">
-        <f>COUNTA(F2:AK2)</f>
+      <c r="AL2" s="4"/>
+      <c r="AM2" s="4">
+        <f>COUNTA(G2:AL2)</f>
         <v>1</v>
       </c>
-      <c r="AM2" s="4">
-        <f>COUNTIF(F2:AK2,"到")</f>
+      <c r="AN2" s="4">
+        <f>COUNTIF(G2:AL2,"到")</f>
         <v>1</v>
       </c>
-      <c r="AN2" s="4">
-        <f>COUNTIF(F2:AK2,"请假")</f>
-        <v>0</v>
-      </c>
       <c r="AO2" s="4">
-        <f>COUNTIF(F2:AK2,"早退")</f>
+        <f>COUNTIF(G2:AL2,"请假")</f>
         <v>0</v>
       </c>
       <c r="AP2" s="4">
-        <f>COUNTIF(F2:AK2,"迟到")</f>
+        <f>COUNTIF(G2:AL2,"早退")</f>
         <v>0</v>
       </c>
       <c r="AQ2" s="4">
-        <f>AM2/AL2</f>
+        <f>COUNTIF(G2:AL2,"迟到")</f>
+        <v>0</v>
+      </c>
+      <c r="AR2" s="4">
+        <f>AN2/AM2</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="16.35" customHeight="1" spans="1:43">
+    <row r="3" ht="16.35" customHeight="1" spans="1:44">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -1437,41 +1444,42 @@
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4"/>
-      <c r="AL3" s="4">
-        <f t="shared" ref="AL3:AL23" si="0">COUNTA(F3:AK3)</f>
+      <c r="AL3" s="4"/>
+      <c r="AM3" s="4">
+        <f t="shared" ref="AM3:AM23" si="0">COUNTA(G3:AL3)</f>
         <v>1</v>
       </c>
-      <c r="AM3" s="4">
-        <f t="shared" ref="AM3:AM23" si="1">COUNTIF(F3:AK3,"到")</f>
-        <v>0</v>
-      </c>
       <c r="AN3" s="4">
-        <f t="shared" ref="AN3:AN23" si="2">COUNTIF(F3:AK3,"请假")</f>
+        <f t="shared" ref="AN3:AN23" si="1">COUNTIF(G3:AL3,"到")</f>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" ref="AO3:AO23" si="2">COUNTIF(G3:AL3,"请假")</f>
         <v>1</v>
       </c>
-      <c r="AO3" s="4">
-        <f t="shared" ref="AO3:AO23" si="3">COUNTIF(F3:AK3,"早退")</f>
-        <v>0</v>
-      </c>
       <c r="AP3" s="4">
-        <f t="shared" ref="AP3:AP23" si="4">COUNTIF(F3:AK3,"迟到")</f>
+        <f t="shared" ref="AP3:AP23" si="3">COUNTIF(G3:AL3,"早退")</f>
         <v>0</v>
       </c>
       <c r="AQ3" s="4">
-        <f t="shared" ref="AQ3:AQ23" si="5">AM3/AL3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="16.35" customHeight="1" spans="1:43">
+        <f t="shared" ref="AQ3:AQ23" si="4">COUNTIF(G3:AL3,"迟到")</f>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <f t="shared" ref="AR3:AR23" si="5">AN3/AM3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="16.35" customHeight="1" spans="1:44">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -1502,41 +1510,42 @@
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="4"/>
-      <c r="AL4" s="4">
+      <c r="AL4" s="4"/>
+      <c r="AM4" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AM4" s="4">
+      <c r="AN4" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN4" s="4">
+      <c r="AO4" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO4" s="4">
+      <c r="AP4" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP4" s="4">
+      <c r="AQ4" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ4" s="4">
+      <c r="AR4" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="16.35" customHeight="1" spans="1:43">
+    <row r="5" ht="16.35" customHeight="1" spans="1:44">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -1567,41 +1576,42 @@
       <c r="AI5" s="4"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="4"/>
-      <c r="AL5" s="4">
+      <c r="AL5" s="4"/>
+      <c r="AM5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AM5" s="4">
+      <c r="AN5" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN5" s="4">
+      <c r="AO5" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO5" s="4">
+      <c r="AP5" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP5" s="4">
+      <c r="AQ5" s="4">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AQ5" s="4">
+      <c r="AR5" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="16.35" customHeight="1" spans="1:43">
+    <row r="6" ht="16.35" customHeight="1" spans="1:44">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -1632,32 +1642,33 @@
       <c r="AI6" s="4"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="4"/>
-      <c r="AL6" s="4">
+      <c r="AL6" s="4"/>
+      <c r="AM6" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AM6" s="4">
+      <c r="AN6" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN6" s="4">
+      <c r="AO6" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO6" s="4">
+      <c r="AP6" s="4">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AP6" s="4">
+      <c r="AQ6" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ6" s="4">
+      <c r="AR6" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="16.35" customHeight="1" spans="1:43">
+    <row r="7" ht="16.35" customHeight="1" spans="1:44">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1695,32 +1706,33 @@
       <c r="AI7" s="4"/>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="4"/>
-      <c r="AL7" s="4">
+      <c r="AL7" s="4"/>
+      <c r="AM7" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM7" s="4">
+      <c r="AN7" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN7" s="4">
+      <c r="AO7" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO7" s="4">
+      <c r="AP7" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP7" s="4">
+      <c r="AQ7" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ7" s="4" t="e">
+      <c r="AR7" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="8" ht="16.35" customHeight="1" spans="1:43">
+    <row r="8" ht="16.35" customHeight="1" spans="1:44">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1758,32 +1770,33 @@
       <c r="AI8" s="4"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="4"/>
-      <c r="AL8" s="4">
+      <c r="AL8" s="4"/>
+      <c r="AM8" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM8" s="4">
+      <c r="AN8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN8" s="4">
+      <c r="AO8" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO8" s="4">
+      <c r="AP8" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP8" s="4">
+      <c r="AQ8" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ8" s="4" t="e">
+      <c r="AR8" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="9" ht="16.35" customHeight="1" spans="1:43">
+    <row r="9" ht="16.35" customHeight="1" spans="1:44">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1821,32 +1834,33 @@
       <c r="AI9" s="4"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="4"/>
-      <c r="AL9" s="4">
+      <c r="AL9" s="4"/>
+      <c r="AM9" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM9" s="4">
+      <c r="AN9" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN9" s="4">
+      <c r="AO9" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO9" s="4">
+      <c r="AP9" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP9" s="4">
+      <c r="AQ9" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ9" s="4" t="e">
+      <c r="AR9" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" ht="16.35" customHeight="1" spans="1:43">
+    <row r="10" ht="16.35" customHeight="1" spans="1:44">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1884,32 +1898,33 @@
       <c r="AI10" s="4"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="4"/>
-      <c r="AL10" s="4">
+      <c r="AL10" s="4"/>
+      <c r="AM10" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM10" s="4">
+      <c r="AN10" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN10" s="4">
+      <c r="AO10" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO10" s="4">
+      <c r="AP10" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP10" s="4">
+      <c r="AQ10" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ10" s="4" t="e">
+      <c r="AR10" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" ht="16.35" customHeight="1" spans="1:43">
+    <row r="11" ht="16.35" customHeight="1" spans="1:44">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1947,32 +1962,33 @@
       <c r="AI11" s="4"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="4"/>
-      <c r="AL11" s="4">
+      <c r="AL11" s="4"/>
+      <c r="AM11" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM11" s="4">
+      <c r="AN11" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN11" s="4">
+      <c r="AO11" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO11" s="4">
+      <c r="AP11" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP11" s="4">
+      <c r="AQ11" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ11" s="4" t="e">
+      <c r="AR11" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" ht="16.35" customHeight="1" spans="1:43">
+    <row r="12" ht="16.35" customHeight="1" spans="1:44">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -2007,35 +2023,36 @@
       <c r="AF12" s="4"/>
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="4"/>
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="3"/>
       <c r="AK12" s="4"/>
-      <c r="AL12" s="4">
+      <c r="AL12" s="4"/>
+      <c r="AM12" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM12" s="4">
+      <c r="AN12" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN12" s="4">
+      <c r="AO12" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO12" s="4">
+      <c r="AP12" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP12" s="4">
+      <c r="AQ12" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ12" s="4" t="e">
+      <c r="AR12" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="13" ht="16.35" customHeight="1" spans="1:43">
+    <row r="13" ht="16.35" customHeight="1" spans="1:44">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -2073,32 +2090,33 @@
       <c r="AI13" s="4"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="4"/>
-      <c r="AL13" s="4">
+      <c r="AL13" s="4"/>
+      <c r="AM13" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM13" s="4">
+      <c r="AN13" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN13" s="4">
+      <c r="AO13" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO13" s="4">
+      <c r="AP13" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP13" s="4">
+      <c r="AQ13" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ13" s="4" t="e">
+      <c r="AR13" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" ht="16.35" customHeight="1" spans="1:43">
+    <row r="14" ht="16.35" customHeight="1" spans="1:44">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -2136,32 +2154,33 @@
       <c r="AI14" s="4"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="4"/>
-      <c r="AL14" s="4">
+      <c r="AL14" s="4"/>
+      <c r="AM14" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="4">
+      <c r="AN14" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="4">
+      <c r="AO14" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO14" s="4">
+      <c r="AP14" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP14" s="4">
+      <c r="AQ14" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ14" s="4" t="e">
+      <c r="AR14" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" ht="16.35" customHeight="1" spans="1:43">
+    <row r="15" ht="16.35" customHeight="1" spans="1:44">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2199,32 +2218,33 @@
       <c r="AI15" s="4"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="4"/>
-      <c r="AL15" s="4">
+      <c r="AL15" s="4"/>
+      <c r="AM15" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM15" s="4">
+      <c r="AN15" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN15" s="4">
+      <c r="AO15" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO15" s="4">
+      <c r="AP15" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="4">
+      <c r="AQ15" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ15" s="4" t="e">
+      <c r="AR15" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" ht="16.35" customHeight="1" spans="1:43">
+    <row r="16" ht="16.35" customHeight="1" spans="1:44">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -2262,32 +2282,33 @@
       <c r="AI16" s="4"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="4"/>
-      <c r="AL16" s="4">
+      <c r="AL16" s="4"/>
+      <c r="AM16" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="4">
+      <c r="AN16" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN16" s="4">
+      <c r="AO16" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO16" s="4">
+      <c r="AP16" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP16" s="4">
+      <c r="AQ16" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ16" s="4" t="e">
+      <c r="AR16" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" ht="16.35" customHeight="1" spans="1:43">
+    <row r="17" ht="16.35" customHeight="1" spans="1:44">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -2325,32 +2346,33 @@
       <c r="AI17" s="4"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="4"/>
-      <c r="AL17" s="4">
+      <c r="AL17" s="4"/>
+      <c r="AM17" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM17" s="4">
+      <c r="AN17" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN17" s="4">
+      <c r="AO17" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO17" s="4">
+      <c r="AP17" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP17" s="4">
+      <c r="AQ17" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ17" s="4" t="e">
+      <c r="AR17" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" ht="16.35" customHeight="1" spans="1:43">
+    <row r="18" ht="16.35" customHeight="1" spans="1:44">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2388,32 +2410,33 @@
       <c r="AI18" s="4"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="4"/>
-      <c r="AL18" s="4">
+      <c r="AL18" s="4"/>
+      <c r="AM18" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM18" s="4">
+      <c r="AN18" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN18" s="4">
+      <c r="AO18" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO18" s="4">
+      <c r="AP18" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP18" s="4">
+      <c r="AQ18" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ18" s="4" t="e">
+      <c r="AR18" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" ht="16.35" customHeight="1" spans="1:43">
+    <row r="19" ht="16.35" customHeight="1" spans="1:44">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2451,32 +2474,33 @@
       <c r="AI19" s="4"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="4"/>
-      <c r="AL19" s="4">
+      <c r="AL19" s="4"/>
+      <c r="AM19" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM19" s="4">
+      <c r="AN19" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="4">
+      <c r="AO19" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO19" s="4">
+      <c r="AP19" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP19" s="4">
+      <c r="AQ19" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ19" s="4" t="e">
+      <c r="AR19" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" ht="16.35" customHeight="1" spans="1:43">
+    <row r="20" ht="16.35" customHeight="1" spans="1:44">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2514,32 +2538,33 @@
       <c r="AI20" s="4"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="4"/>
-      <c r="AL20" s="4">
+      <c r="AL20" s="4"/>
+      <c r="AM20" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM20" s="4">
+      <c r="AN20" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN20" s="4">
+      <c r="AO20" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO20" s="4">
+      <c r="AP20" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP20" s="4">
+      <c r="AQ20" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ20" s="4" t="e">
+      <c r="AR20" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" ht="16.35" customHeight="1" spans="1:43">
+    <row r="21" ht="16.35" customHeight="1" spans="1:44">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2577,32 +2602,33 @@
       <c r="AI21" s="4"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="4"/>
-      <c r="AL21" s="4">
+      <c r="AL21" s="4"/>
+      <c r="AM21" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM21" s="4">
+      <c r="AN21" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN21" s="4">
+      <c r="AO21" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO21" s="4">
+      <c r="AP21" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP21" s="4">
+      <c r="AQ21" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ21" s="4" t="e">
+      <c r="AR21" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" ht="16.35" customHeight="1" spans="1:43">
+    <row r="22" ht="16.35" customHeight="1" spans="1:44">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -2640,32 +2666,33 @@
       <c r="AI22" s="4"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="4"/>
-      <c r="AL22" s="4">
+      <c r="AL22" s="4"/>
+      <c r="AM22" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM22" s="4">
+      <c r="AN22" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN22" s="4">
+      <c r="AO22" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO22" s="4">
+      <c r="AP22" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP22" s="4">
+      <c r="AQ22" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ22" s="4" t="e">
+      <c r="AR22" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" ht="16.35" customHeight="1" spans="1:43">
+    <row r="23" ht="16.35" customHeight="1" spans="1:44">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -2703,33 +2730,33 @@
       <c r="AI23" s="4"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="4"/>
-      <c r="AL23" s="4">
+      <c r="AL23" s="4"/>
+      <c r="AM23" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM23" s="4">
+      <c r="AN23" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="4">
+      <c r="AO23" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO23" s="4">
+      <c r="AP23" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP23" s="4">
+      <c r="AQ23" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AQ23" s="4" t="e">
+      <c r="AR23" s="4" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="1:43">
-      <c r="E24" s="5"/>
+    <row r="24" spans="1:44">
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -2759,52 +2786,53 @@
       <c r="AF24" s="5"/>
       <c r="AG24" s="5"/>
       <c r="AH24" s="5"/>
-      <c r="AI24" s="6"/>
-      <c r="AJ24" s="5"/>
+      <c r="AI24" s="5"/>
+      <c r="AJ24" s="6"/>
       <c r="AK24" s="5"/>
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
-      <c r="AO24" s="7"/>
+      <c r="AO24" s="5"/>
       <c r="AP24" s="7"/>
-      <c r="AQ24" s="5"/>
-    </row>
-    <row r="25" spans="1:43">
-      <c r="AI25" s="6"/>
-      <c r="AO25" s="7"/>
+      <c r="AQ24" s="7"/>
+      <c r="AR24" s="5"/>
+    </row>
+    <row r="25" spans="1:44">
+      <c r="AJ25" s="6"/>
       <c r="AP25" s="7"/>
-    </row>
-    <row r="26" spans="1:43">
-      <c r="AI26" s="6"/>
-      <c r="AO26" s="7"/>
+      <c r="AQ25" s="7"/>
+    </row>
+    <row r="26" spans="1:44">
+      <c r="AJ26" s="6"/>
       <c r="AP26" s="7"/>
-    </row>
-    <row r="27" spans="1:43">
-      <c r="AI27" s="6"/>
-    </row>
-    <row r="28" spans="1:43">
-      <c r="AI28" s="6"/>
-    </row>
-    <row r="29" spans="1:43">
-      <c r="AI29" s="6"/>
-    </row>
-    <row r="30" spans="1:43">
-      <c r="AI30" s="6"/>
-    </row>
-    <row r="31" spans="1:43">
-      <c r="AI31" s="6"/>
-    </row>
-    <row r="32" spans="1:43">
-      <c r="AI32" s="6"/>
-    </row>
-    <row r="33" spans="35:35">
-      <c r="AI33" s="6"/>
-    </row>
-    <row r="34" spans="35:35">
-      <c r="AI34" s="6"/>
-    </row>
-    <row r="35" spans="35:35">
-      <c r="AI35" s="5"/>
+      <c r="AQ26" s="7"/>
+    </row>
+    <row r="27" spans="1:44">
+      <c r="AJ27" s="6"/>
+    </row>
+    <row r="28" spans="1:44">
+      <c r="AJ28" s="6"/>
+    </row>
+    <row r="29" spans="1:44">
+      <c r="AJ29" s="6"/>
+    </row>
+    <row r="30" spans="1:44">
+      <c r="AJ30" s="6"/>
+    </row>
+    <row r="31" spans="1:44">
+      <c r="AJ31" s="6"/>
+    </row>
+    <row r="32" spans="1:44">
+      <c r="AJ32" s="6"/>
+    </row>
+    <row r="33" spans="36:36">
+      <c r="AJ33" s="6"/>
+    </row>
+    <row r="34" spans="36:36">
+      <c r="AJ34" s="6"/>
+    </row>
+    <row r="35" spans="36:36">
+      <c r="AJ35" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
